--- a/production-planning/기준정보.xlsx
+++ b/production-planning/기준정보.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PIXIT_USER3\OneDrive\Desktop\생산계획생성\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71BF27F7-B576-4CE9-8959-FE5A45EC3566}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DCCE8CE-99C7-42BC-A0C0-C1B804824ACE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="851" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11295" tabRatio="851" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CAPA" sheetId="1" r:id="rId1"/>
@@ -25,12 +25,25 @@
     <sheet name="휴무" sheetId="10" r:id="rId10"/>
     <sheet name="설정" sheetId="11" r:id="rId11"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="100">
   <si>
     <t>NO</t>
   </si>
@@ -321,12 +334,6 @@
   </si>
   <si>
     <t>당일 브리핑 시각 (후속)</t>
-  </si>
-  <si>
-    <t>WEBHOOK_URL</t>
-  </si>
-  <si>
-    <t>Google Chat 웹훅 — 계획 갱신·이월/납기 알림 발송용. 실주소는 커밋 금지: 리허설 사본·GAS 스크립트 속성(CHAT_WEBHOOK_URL)에만 보관</t>
   </si>
   <si>
     <t>ORDER_SOURCE_FOLDER_ID</t>
@@ -348,7 +355,7 @@
     <numFmt numFmtId="176" formatCode="yyyy&quot;-&quot;mm&quot;-&quot;dd"/>
     <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -382,11 +389,6 @@
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -428,11 +430,11 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
-    <xf numFmtId="41" fontId="6" fillId="0" borderId="1">
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -470,7 +472,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="41" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -791,16 +792,16 @@
       <c r="J2" s="3">
         <v>22.8</v>
       </c>
-      <c r="K2" s="14">
+      <c r="K2" s="13">
         <v>7224</v>
       </c>
       <c r="L2" s="3">
         <v>23</v>
       </c>
-      <c r="M2" s="14">
+      <c r="M2" s="13">
         <v>562</v>
       </c>
-      <c r="N2" s="14">
+      <c r="N2" s="13">
         <v>129800</v>
       </c>
       <c r="O2" s="3">
@@ -841,16 +842,16 @@
       <c r="J3" s="3">
         <v>24.9</v>
       </c>
-      <c r="K3" s="14">
+      <c r="K3" s="13">
         <v>6992</v>
       </c>
       <c r="L3" s="3">
         <v>35</v>
       </c>
-      <c r="M3" s="14">
+      <c r="M3" s="13">
         <v>834</v>
       </c>
-      <c r="N3" s="14">
+      <c r="N3" s="13">
         <v>85000</v>
       </c>
       <c r="O3" s="3">
@@ -891,16 +892,16 @@
       <c r="J4" s="3">
         <v>22.8</v>
       </c>
-      <c r="K4" s="14">
+      <c r="K4" s="13">
         <v>4751</v>
       </c>
       <c r="L4" s="3">
         <v>21</v>
       </c>
-      <c r="M4" s="14">
+      <c r="M4" s="13">
         <v>499</v>
       </c>
-      <c r="N4" s="14">
+      <c r="N4" s="13">
         <v>94000</v>
       </c>
       <c r="O4" s="3">
@@ -941,16 +942,16 @@
       <c r="J5" s="3">
         <v>18.399999999999999</v>
       </c>
-      <c r="K5" s="14">
+      <c r="K5" s="13">
         <v>5236</v>
       </c>
       <c r="L5" s="3">
         <v>18</v>
       </c>
-      <c r="M5" s="14">
+      <c r="M5" s="13">
         <v>425</v>
       </c>
-      <c r="N5" s="14">
+      <c r="N5" s="13">
         <v>130000</v>
       </c>
       <c r="O5" s="3">
@@ -991,16 +992,16 @@
       <c r="J6" s="3">
         <v>16.600000000000001</v>
       </c>
-      <c r="K6" s="14">
+      <c r="K6" s="13">
         <v>4552</v>
       </c>
       <c r="L6" s="3">
         <v>25</v>
       </c>
-      <c r="M6" s="14">
+      <c r="M6" s="13">
         <v>589</v>
       </c>
-      <c r="N6" s="14">
+      <c r="N6" s="13">
         <v>85000</v>
       </c>
       <c r="O6" s="3">
@@ -1041,16 +1042,16 @@
       <c r="J7" s="3">
         <v>21.3</v>
       </c>
-      <c r="K7" s="14">
+      <c r="K7" s="13">
         <v>4562</v>
       </c>
       <c r="L7" s="3">
         <v>30</v>
       </c>
-      <c r="M7" s="14">
+      <c r="M7" s="13">
         <v>719</v>
       </c>
-      <c r="N7" s="14">
+      <c r="N7" s="13">
         <v>65000</v>
       </c>
       <c r="O7" s="3">
@@ -1091,16 +1092,16 @@
       <c r="J8" s="3">
         <v>24.4</v>
       </c>
-      <c r="K8" s="14">
+      <c r="K8" s="13">
         <v>4685</v>
       </c>
       <c r="L8" s="3">
         <v>29</v>
       </c>
-      <c r="M8" s="14">
+      <c r="M8" s="13">
         <v>702</v>
       </c>
-      <c r="N8" s="14">
+      <c r="N8" s="13">
         <v>62300</v>
       </c>
       <c r="O8" s="3">
@@ -1141,16 +1142,16 @@
       <c r="J9" s="3">
         <v>14.4</v>
       </c>
-      <c r="K9" s="14">
+      <c r="K9" s="13">
         <v>2696</v>
       </c>
       <c r="L9" s="3">
         <v>47</v>
       </c>
-      <c r="M9" s="14">
+      <c r="M9" s="13">
         <v>1123</v>
       </c>
-      <c r="N9" s="14">
+      <c r="N9" s="13">
         <v>24500</v>
       </c>
       <c r="O9" s="3">
@@ -2416,7 +2417,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="A1:C1000"/>
+  <dimension ref="A1:C999"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.28515625" style="1" bestFit="1" customWidth="1"/>
@@ -2479,28 +2480,20 @@
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="13" t="s">
+      <c r="A6" t="s">
         <v>97</v>
       </c>
-      <c r="B6" s="13"/>
-      <c r="C6" s="13" t="s">
+      <c r="B6" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C6" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>99</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="C7" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="4"/>
-    </row>
+    <row r="10" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="4"/>
+    </row>
+    <row r="20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="22" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -3480,7 +3473,6 @@
     <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
